--- a/SuppXLS/Scen_UC_ELC_MANHEAT_20_50.xlsx
+++ b/SuppXLS/Scen_UC_ELC_MANHEAT_20_50.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930B6B1B-E394-4078-9CC7-894BA0C3F57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C9D3D9-DFC2-4DEB-A126-F690E58223B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>UC - Each Region/Period</t>
   </si>
@@ -98,12 +98,6 @@
     <t>MANHEAT</t>
   </si>
   <si>
-    <t>Minimum RENHEATpenetration for process heat</t>
-  </si>
-  <si>
-    <t>Minimum RENHEAT penetration for process heat</t>
-  </si>
-  <si>
     <t>DMD</t>
   </si>
   <si>
@@ -111,6 +105,12 @@
   </si>
   <si>
     <t>ELC</t>
+  </si>
+  <si>
+    <t>Minimum ELC penetration for process heat</t>
+  </si>
+  <si>
+    <t>UC_COMPRD</t>
   </si>
 </sst>
 </file>
@@ -711,18 +711,21 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>19</v>
       </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
       <c r="I6">
         <v>2030</v>
       </c>
@@ -742,23 +745,26 @@
         <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
         <v>19</v>
       </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
       <c r="I7">
         <v>2050</v>
       </c>
@@ -778,7 +784,7 @@
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_UC_ELC_MANHEAT_20_50.xlsx
+++ b/SuppXLS/Scen_UC_ELC_MANHEAT_20_50.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C9D3D9-DFC2-4DEB-A126-F690E58223B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5DF4CC-DF70-4185-A345-A23AE5B6EF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC_MANHEAT_20_50" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>UC - Each Region/Period</t>
   </si>
@@ -108,9 +108,6 @@
   </si>
   <si>
     <t>Minimum ELC penetration for process heat</t>
-  </si>
-  <si>
-    <t>UC_COMPRD</t>
   </si>
 </sst>
 </file>
@@ -723,9 +720,6 @@
       <c r="G6" t="s">
         <v>19</v>
       </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
       <c r="I6">
         <v>2030</v>
       </c>
@@ -761,9 +755,6 @@
       </c>
       <c r="G7" t="s">
         <v>19</v>
-      </c>
-      <c r="H7" t="s">
-        <v>24</v>
       </c>
       <c r="I7">
         <v>2050</v>

--- a/SuppXLS/Scen_UC_ELC_MANHEAT_20_50.xlsx
+++ b/SuppXLS/Scen_UC_ELC_MANHEAT_20_50.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5DF4CC-DF70-4185-A345-A23AE5B6EF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CB53FF-08DC-444F-A861-10A923B62CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC_MANHEAT_20_50" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>UC - Each Region/Period</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Minimum ELC penetration for process heat</t>
+  </si>
+  <si>
+    <t>UC_COMPRD</t>
   </si>
 </sst>
 </file>
@@ -720,6 +723,9 @@
       <c r="G6" t="s">
         <v>19</v>
       </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
       <c r="I6">
         <v>2030</v>
       </c>
@@ -755,6 +761,9 @@
       </c>
       <c r="G7" t="s">
         <v>19</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
       </c>
       <c r="I7">
         <v>2050</v>

--- a/SuppXLS/Scen_UC_ELC_MANHEAT_20_50.xlsx
+++ b/SuppXLS/Scen_UC_ELC_MANHEAT_20_50.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CB53FF-08DC-444F-A861-10A923B62CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B104066E-B13F-44ED-AF1B-42AFF14BB035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC_MANHEAT_20_50" sheetId="1" r:id="rId1"/>
@@ -638,6 +638,7 @@
     <col min="3" max="3" width="8.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
